--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N47_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N47_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>82.63848434950938</v>
+        <v>13.42875370679528</v>
       </c>
       <c r="D2" t="n">
-        <v>83.8694337402746</v>
+        <v>13.62878298279462</v>
       </c>
       <c r="E2" t="n">
-        <v>20.27550452891083</v>
+        <v>3.29476948594801</v>
       </c>
       <c r="F2" t="n">
-        <v>21.79088133742204</v>
+        <v>3.541018217331082</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>74.11917411833318</v>
+        <v>12.04436579422914</v>
       </c>
       <c r="D3" t="n">
-        <v>75.33756475212569</v>
+        <v>12.24235427222042</v>
       </c>
       <c r="E3" t="n">
-        <v>20.27550452891083</v>
+        <v>3.29476948594801</v>
       </c>
       <c r="F3" t="n">
-        <v>21.79088133742204</v>
+        <v>3.541018217331082</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>65.33502857472311</v>
+        <v>10.61694214339251</v>
       </c>
       <c r="D4" t="n">
-        <v>66.59155862520268</v>
+        <v>10.82112827659544</v>
       </c>
       <c r="E4" t="n">
-        <v>20.27550452891083</v>
+        <v>3.29476948594801</v>
       </c>
       <c r="F4" t="n">
-        <v>21.79088133742204</v>
+        <v>3.541018217331082</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>51.68311434844553</v>
+        <v>8.398506081622399</v>
       </c>
       <c r="D5" t="n">
-        <v>52.95066079268715</v>
+        <v>8.604482378811662</v>
       </c>
       <c r="E5" t="n">
-        <v>20.27550452891083</v>
+        <v>3.29476948594801</v>
       </c>
       <c r="F5" t="n">
-        <v>21.79088133742204</v>
+        <v>3.541018217331082</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>41.2468200643901</v>
+        <v>6.702608260463392</v>
       </c>
       <c r="D6" t="n">
-        <v>41.56909887786414</v>
+        <v>6.754978567652923</v>
       </c>
       <c r="E6" t="n">
-        <v>20.27550452891083</v>
+        <v>3.29476948594801</v>
       </c>
       <c r="F6" t="n">
-        <v>21.79088133742204</v>
+        <v>3.541018217331082</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>27.94571780153165</v>
+        <v>4.541179142748893</v>
       </c>
       <c r="D7" t="n">
-        <v>28.04372064921889</v>
+        <v>4.557104605498069</v>
       </c>
       <c r="E7" t="n">
-        <v>20.27550452891083</v>
+        <v>3.29476948594801</v>
       </c>
       <c r="F7" t="n">
-        <v>21.79088133742204</v>
+        <v>3.541018217331082</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>32.97408305593363</v>
+        <v>5.358288496589216</v>
       </c>
       <c r="D8" t="n">
-        <v>34.50617116840098</v>
+        <v>5.607252814865158</v>
       </c>
       <c r="E8" t="n">
-        <v>20.27550452891083</v>
+        <v>3.29476948594801</v>
       </c>
       <c r="F8" t="n">
-        <v>21.79088133742204</v>
+        <v>3.541018217331082</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>24.7486007644748</v>
+        <v>4.021647624227155</v>
       </c>
       <c r="D9" t="n">
-        <v>26.54952336844986</v>
+        <v>4.314297547373102</v>
       </c>
       <c r="E9" t="n">
-        <v>20.27550452891083</v>
+        <v>3.29476948594801</v>
       </c>
       <c r="F9" t="n">
-        <v>21.79088133742204</v>
+        <v>3.541018217331082</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>39.77462932602628</v>
+        <v>6.463377265479271</v>
       </c>
       <c r="D10" t="n">
-        <v>41.51967412831947</v>
+        <v>6.746947045851915</v>
       </c>
       <c r="E10" t="n">
-        <v>20.27550452891083</v>
+        <v>3.29476948594801</v>
       </c>
       <c r="F10" t="n">
-        <v>21.79088133742204</v>
+        <v>3.541018217331082</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>25.38390721772753</v>
+        <v>4.124884922880725</v>
       </c>
       <c r="D11" t="n">
-        <v>32.3657513436571</v>
+        <v>5.259434593344278</v>
       </c>
       <c r="E11" t="n">
-        <v>20.27550452891083</v>
+        <v>3.29476948594801</v>
       </c>
       <c r="F11" t="n">
-        <v>21.79088133742204</v>
+        <v>3.541018217331082</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>23.31794691672545</v>
+        <v>3.789166373967886</v>
       </c>
       <c r="D12" t="n">
-        <v>21.60953304114586</v>
+        <v>3.511549119186202</v>
       </c>
       <c r="E12" t="n">
-        <v>20.27550452891083</v>
+        <v>3.29476948594801</v>
       </c>
       <c r="F12" t="n">
-        <v>21.79088133742204</v>
+        <v>3.541018217331082</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>25.33623301375955</v>
+        <v>4.117137864735927</v>
       </c>
       <c r="D13" t="n">
-        <v>25.50073654831945</v>
+        <v>4.143869689101911</v>
       </c>
       <c r="E13" t="n">
-        <v>20.27550452891083</v>
+        <v>3.29476948594801</v>
       </c>
       <c r="F13" t="n">
-        <v>21.79088133742204</v>
+        <v>3.541018217331082</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>24.13803665977949</v>
+        <v>3.922430957214167</v>
       </c>
       <c r="D14" t="n">
-        <v>18.58699340213846</v>
+        <v>3.0203864278475</v>
       </c>
       <c r="E14" t="n">
-        <v>20.27550452891083</v>
+        <v>3.29476948594801</v>
       </c>
       <c r="F14" t="n">
-        <v>21.79088133742204</v>
+        <v>3.541018217331082</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>23.56329759817102</v>
+        <v>3.829035859702791</v>
       </c>
       <c r="D15" t="n">
-        <v>23.43077059727226</v>
+        <v>3.807500222056742</v>
       </c>
       <c r="E15" t="n">
-        <v>20.27550452891083</v>
+        <v>3.29476948594801</v>
       </c>
       <c r="F15" t="n">
-        <v>21.79088133742204</v>
+        <v>3.541018217331082</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>18.79447172315673</v>
+        <v>3.054101655012968</v>
       </c>
       <c r="D16" t="n">
-        <v>18.95113201536846</v>
+        <v>3.079558952497374</v>
       </c>
       <c r="E16" t="n">
-        <v>20.27550452891083</v>
+        <v>3.29476948594801</v>
       </c>
       <c r="F16" t="n">
-        <v>21.79088133742204</v>
+        <v>3.541018217331082</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>13.00145080012586</v>
+        <v>2.112735755020453</v>
       </c>
       <c r="D17" t="n">
-        <v>13.18623851389792</v>
+        <v>2.142763758508412</v>
       </c>
       <c r="E17" t="n">
-        <v>20.27550452891083</v>
+        <v>3.29476948594801</v>
       </c>
       <c r="F17" t="n">
-        <v>21.79088133742204</v>
+        <v>3.541018217331082</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>41.31134275062463</v>
+        <v>6.713093196976502</v>
       </c>
       <c r="D18" t="n">
-        <v>41.65798620134483</v>
+        <v>6.769422757718535</v>
       </c>
       <c r="E18" t="n">
-        <v>20.27550452891083</v>
+        <v>3.29476948594801</v>
       </c>
       <c r="F18" t="n">
-        <v>21.79088133742204</v>
+        <v>3.541018217331082</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>51.98187353263798</v>
+        <v>8.447054449053672</v>
       </c>
       <c r="D19" t="n">
-        <v>52.61558931680112</v>
+        <v>8.550033263980183</v>
       </c>
       <c r="E19" t="n">
-        <v>20.27550452891083</v>
+        <v>3.29476948594801</v>
       </c>
       <c r="F19" t="n">
-        <v>21.79088133742204</v>
+        <v>3.541018217331082</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>23.98840217437935</v>
+        <v>3.898115353336645</v>
       </c>
       <c r="D20" t="n">
-        <v>4.338280040603389</v>
+        <v>0.7049705065980508</v>
       </c>
       <c r="E20" t="n">
-        <v>20.27550452891083</v>
+        <v>3.29476948594801</v>
       </c>
       <c r="F20" t="n">
-        <v>21.79088133742204</v>
+        <v>3.541018217331082</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>20.31560409482482</v>
+        <v>3.301285665409033</v>
       </c>
       <c r="D21" t="n">
-        <v>14.87620336684723</v>
+        <v>2.417383047112675</v>
       </c>
       <c r="E21" t="n">
-        <v>20.27550452891083</v>
+        <v>3.29476948594801</v>
       </c>
       <c r="F21" t="n">
-        <v>21.79088133742204</v>
+        <v>3.541018217331082</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>48.75332059467778</v>
+        <v>7.922414596635139</v>
       </c>
       <c r="D22" t="n">
-        <v>48.9303253770419</v>
+        <v>7.95117787376931</v>
       </c>
       <c r="E22" t="n">
-        <v>20.27550452891083</v>
+        <v>3.29476948594801</v>
       </c>
       <c r="F22" t="n">
-        <v>21.79088133742204</v>
+        <v>3.541018217331082</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>9.593300182433442</v>
+        <v>1.558911279645434</v>
       </c>
       <c r="D23" t="n">
-        <v>9.332452229246634</v>
+        <v>1.516523487252578</v>
       </c>
       <c r="E23" t="n">
-        <v>20.27550452891083</v>
+        <v>3.29476948594801</v>
       </c>
       <c r="F23" t="n">
-        <v>21.79088133742204</v>
+        <v>3.541018217331082</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>64.8026784404603</v>
+        <v>10.5304352465748</v>
       </c>
       <c r="D24" t="n">
-        <v>64.97806484531169</v>
+        <v>10.55893553736315</v>
       </c>
       <c r="E24" t="n">
-        <v>20.27550452891083</v>
+        <v>3.29476948594801</v>
       </c>
       <c r="F24" t="n">
-        <v>21.79088133742204</v>
+        <v>3.541018217331082</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>71.26194263703913</v>
+        <v>11.58006567851886</v>
       </c>
       <c r="D25" t="n">
-        <v>71.71960546034467</v>
+        <v>11.65443588730601</v>
       </c>
       <c r="E25" t="n">
-        <v>20.27550452891083</v>
+        <v>3.29476948594801</v>
       </c>
       <c r="F25" t="n">
-        <v>21.79088133742204</v>
+        <v>3.541018217331082</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>19.59817523805983</v>
+        <v>3.184703476184722</v>
       </c>
       <c r="D26" t="n">
-        <v>19.24647781891672</v>
+        <v>3.127552645573968</v>
       </c>
       <c r="E26" t="n">
-        <v>20.27550452891083</v>
+        <v>3.29476948594801</v>
       </c>
       <c r="F26" t="n">
-        <v>21.79088133742204</v>
+        <v>3.541018217331082</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
